--- a/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/30gps/3mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/30gps/3mps_analysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Time</t>
   </si>
@@ -79,13 +79,34 @@
     <t>Q</t>
   </si>
   <si>
-    <t>rolling_std</t>
-  </si>
-  <si>
     <t>steady_state</t>
   </si>
   <si>
-    <t>avg_Q_steady</t>
+    <t>Averages</t>
+  </si>
+  <si>
+    <t>RTD_OUT_unc</t>
+  </si>
+  <si>
+    <t>RTD_IN_unc</t>
+  </si>
+  <si>
+    <t>RTD_unc</t>
+  </si>
+  <si>
+    <t>Delta_RTD</t>
+  </si>
+  <si>
+    <t>Rel_unc</t>
+  </si>
+  <si>
+    <t>ABS_unc</t>
+  </si>
+  <si>
+    <t>Average Q (W)</t>
+  </si>
+  <si>
+    <t>Average Q Uncertainty (W)</t>
   </si>
 </sst>
 </file>
@@ -421,10 +442,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,8 +518,23 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:29">
       <c r="A2" s="1">
         <v>46068.64970356481</v>
       </c>
@@ -562,14 +598,32 @@
       <c r="U2">
         <v>574.366221860275</v>
       </c>
-      <c r="W2" t="b">
-        <v>0</v>
+      <c r="V2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W2" t="s">
+        <v>29</v>
       </c>
       <c r="X2">
-        <v>567.4625195742776</v>
+        <v>0.253771754</v>
+      </c>
+      <c r="Y2">
+        <v>0.262609344</v>
+      </c>
+      <c r="Z2">
+        <v>0.365190047351166</v>
+      </c>
+      <c r="AA2">
+        <v>4.418794999999996</v>
+      </c>
+      <c r="AB2">
+        <v>0.08324751462043399</v>
+      </c>
+      <c r="AC2">
+        <v>47.81456045179667</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:29">
       <c r="A3" s="1">
         <v>46068.64981930555</v>
       </c>
@@ -633,11 +687,32 @@
       <c r="U3">
         <v>565.5925422529781</v>
       </c>
-      <c r="W3" t="b">
-        <v>0</v>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>567.5354051641807</v>
+      </c>
+      <c r="X3">
+        <v>0.253816582</v>
+      </c>
+      <c r="Y3">
+        <v>0.262647544</v>
+      </c>
+      <c r="Z3">
+        <v>0.3652486682623151</v>
+      </c>
+      <c r="AA3">
+        <v>4.415481</v>
+      </c>
+      <c r="AB3">
+        <v>0.08332227430461023</v>
+      </c>
+      <c r="AC3">
+        <v>47.12645695024449</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:29">
       <c r="A4" s="1">
         <v>46068.649935625</v>
       </c>
@@ -701,14 +776,32 @@
       <c r="U4">
         <v>566.7391401536875</v>
       </c>
-      <c r="V4">
-        <v>4.769076010374348</v>
-      </c>
-      <c r="W4" t="b">
-        <v>0</v>
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="s">
+        <v>30</v>
+      </c>
+      <c r="X4">
+        <v>0.253854418</v>
+      </c>
+      <c r="Y4">
+        <v>0.262682244</v>
+      </c>
+      <c r="Z4">
+        <v>0.3652999135655445</v>
+      </c>
+      <c r="AA4">
+        <v>4.413913000000001</v>
+      </c>
+      <c r="AB4">
+        <v>0.08336297357024973</v>
+      </c>
+      <c r="AC4">
+        <v>47.2450599618579</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:29">
       <c r="A5" s="1">
         <v>46068.65005136574</v>
       </c>
@@ -772,14 +865,32 @@
       <c r="U5">
         <v>568.8908741961133</v>
       </c>
-      <c r="V5">
-        <v>1.674496926559631</v>
-      </c>
-      <c r="W5" t="b">
+      <c r="V5" t="b">
         <v>1</v>
       </c>
+      <c r="W5">
+        <v>47.28652498182681</v>
+      </c>
+      <c r="X5">
+        <v>0.253893524</v>
+      </c>
+      <c r="Y5">
+        <v>0.26272172</v>
+      </c>
+      <c r="Z5">
+        <v>0.36535547578885</v>
+      </c>
+      <c r="AA5">
+        <v>4.414098000000003</v>
+      </c>
+      <c r="AB5">
+        <v>0.08337202656676021</v>
+      </c>
+      <c r="AC5">
+        <v>47.42958507706579</v>
+      </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:29">
       <c r="A6" s="1">
         <v>46068.65016710648</v>
       </c>
@@ -843,14 +954,29 @@
       <c r="U6">
         <v>565.0811936299013</v>
       </c>
-      <c r="V6">
-        <v>1.910166313947407</v>
-      </c>
-      <c r="W6" t="b">
+      <c r="V6" t="b">
         <v>1</v>
       </c>
+      <c r="X6">
+        <v>0.253933268</v>
+      </c>
+      <c r="Y6">
+        <v>0.262765972</v>
+      </c>
+      <c r="Z6">
+        <v>0.3654149157304127</v>
+      </c>
+      <c r="AA6">
+        <v>4.416352000000003</v>
+      </c>
+      <c r="AB6">
+        <v>0.08334344961790839</v>
+      </c>
+      <c r="AC6">
+        <v>47.09581599132122</v>
+      </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:29">
       <c r="A7" s="1">
         <v>46068.65028342592</v>
       </c>
@@ -914,14 +1040,29 @@
       <c r="U7">
         <v>566.3602511995026</v>
       </c>
-      <c r="V7">
-        <v>1.938801478314934</v>
-      </c>
-      <c r="W7" t="b">
+      <c r="V7" t="b">
         <v>1</v>
       </c>
+      <c r="X7">
+        <v>0.253966334</v>
+      </c>
+      <c r="Y7">
+        <v>0.262796852</v>
+      </c>
+      <c r="Z7">
+        <v>0.3654600993631308</v>
+      </c>
+      <c r="AA7">
+        <v>4.415258999999999</v>
+      </c>
+      <c r="AB7">
+        <v>0.08337394398295725</v>
+      </c>
+      <c r="AC7">
+        <v>47.21968785768092</v>
+      </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:29">
       <c r="A8" s="1">
         <v>46068.65039974537</v>
       </c>
@@ -985,14 +1126,29 @@
       <c r="U8">
         <v>569.0020214800093</v>
       </c>
-      <c r="V8">
-        <v>1.999492832007628</v>
-      </c>
-      <c r="W8" t="b">
+      <c r="V8" t="b">
         <v>1</v>
       </c>
+      <c r="X8">
+        <v>0.253999718</v>
+      </c>
+      <c r="Y8">
+        <v>0.262833144</v>
+      </c>
+      <c r="Z8">
+        <v>0.3655093956781471</v>
+      </c>
+      <c r="AA8">
+        <v>4.416713000000001</v>
+      </c>
+      <c r="AB8">
+        <v>0.08335797255282701</v>
+      </c>
+      <c r="AC8">
+        <v>47.4308548890337</v>
+      </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:29">
       <c r="A9" s="1">
         <v>46068.65051548611</v>
       </c>
@@ -1056,14 +1212,29 @@
       <c r="U9">
         <v>564.9069668501051</v>
       </c>
-      <c r="V9">
-        <v>2.076072334845567</v>
-      </c>
-      <c r="W9" t="b">
+      <c r="V9" t="b">
         <v>1</v>
       </c>
+      <c r="X9">
+        <v>0.254028652</v>
+      </c>
+      <c r="Y9">
+        <v>0.262869438</v>
+      </c>
+      <c r="Z9">
+        <v>0.3655556010668869</v>
+      </c>
+      <c r="AA9">
+        <v>4.420393000000004</v>
+      </c>
+      <c r="AB9">
+        <v>0.08329995290651258</v>
+      </c>
+      <c r="AC9">
+        <v>47.05672373517461</v>
+      </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:29">
       <c r="A10" s="1">
         <v>46068.65063180555</v>
       </c>
@@ -1127,14 +1298,29 @@
       <c r="U10">
         <v>565.2638449459613</v>
       </c>
-      <c r="V10">
-        <v>2.268288569123718</v>
-      </c>
-      <c r="W10" t="b">
+      <c r="V10" t="b">
         <v>1</v>
       </c>
+      <c r="X10">
+        <v>0.25406776</v>
+      </c>
+      <c r="Y10">
+        <v>0.262910506</v>
+      </c>
+      <c r="Z10">
+        <v>0.3656123094708295</v>
+      </c>
+      <c r="AA10">
+        <v>4.421372999999996</v>
+      </c>
+      <c r="AB10">
+        <v>0.08329448872653593</v>
+      </c>
+      <c r="AC10">
+        <v>47.08336296036973</v>
+      </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:29">
       <c r="A11" s="1">
         <v>46068.65074754629</v>
       </c>
@@ -1198,14 +1384,29 @@
       <c r="U11">
         <v>573.0024309873552</v>
       </c>
-      <c r="V11">
-        <v>4.57437819987325</v>
-      </c>
-      <c r="W11" t="b">
-        <v>0</v>
+      <c r="V11" t="b">
+        <v>1</v>
+      </c>
+      <c r="X11">
+        <v>0.254104642</v>
+      </c>
+      <c r="Y11">
+        <v>0.262951256</v>
+      </c>
+      <c r="Z11">
+        <v>0.3656672423364249</v>
+      </c>
+      <c r="AA11">
+        <v>4.423307000000001</v>
+      </c>
+      <c r="AB11">
+        <v>0.08327092402706661</v>
+      </c>
+      <c r="AC11">
+        <v>47.71444189807253</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:29">
       <c r="A12" s="1">
         <v>46068.65086386574</v>
       </c>
@@ -1269,14 +1470,29 @@
       <c r="U12">
         <v>558.5856891700219</v>
       </c>
-      <c r="V12">
-        <v>7.214868018143913</v>
-      </c>
-      <c r="W12" t="b">
-        <v>0</v>
+      <c r="V12" t="b">
+        <v>1</v>
+      </c>
+      <c r="X12">
+        <v>0.254154242</v>
+      </c>
+      <c r="Y12">
+        <v>0.26298755</v>
+      </c>
+      <c r="Z12">
+        <v>0.3657278088710196</v>
+      </c>
+      <c r="AA12">
+        <v>4.416654000000001</v>
+      </c>
+      <c r="AB12">
+        <v>0.08340816533836465</v>
+      </c>
+      <c r="AC12">
+        <v>46.59060751793755</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:29">
       <c r="A13" s="1">
         <v>46068.65098018519</v>
       </c>
@@ -1340,14 +1556,29 @@
       <c r="U13">
         <v>573.9955201990126</v>
       </c>
-      <c r="V13">
-        <v>8.624495764506994</v>
-      </c>
-      <c r="W13" t="b">
-        <v>0</v>
+      <c r="V13" t="b">
+        <v>1</v>
+      </c>
+      <c r="X13">
+        <v>0.254181586</v>
+      </c>
+      <c r="Y13">
+        <v>0.263022252</v>
+      </c>
+      <c r="Z13">
+        <v>0.3657717645043517</v>
+      </c>
+      <c r="AA13">
+        <v>4.420332999999999</v>
+      </c>
+      <c r="AB13">
+        <v>0.08334961592624177</v>
+      </c>
+      <c r="AC13">
+        <v>47.84230615197105</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:29">
       <c r="A14" s="1">
         <v>46068.65109592592</v>
       </c>
@@ -1411,14 +1642,29 @@
       <c r="U14">
         <v>564.1403515831117</v>
       </c>
-      <c r="V14">
-        <v>7.804288514584744</v>
-      </c>
-      <c r="W14" t="b">
-        <v>0</v>
+      <c r="V14" t="b">
+        <v>1</v>
+      </c>
+      <c r="X14">
+        <v>0.254209568</v>
+      </c>
+      <c r="Y14">
+        <v>0.263055998</v>
+      </c>
+      <c r="Z14">
+        <v>0.3658154760894113</v>
+      </c>
+      <c r="AA14">
+        <v>4.423214999999999</v>
+      </c>
+      <c r="AB14">
+        <v>0.08330590127897355</v>
+      </c>
+      <c r="AC14">
+        <v>46.99622043646814</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:29">
       <c r="A15" s="1">
         <v>46068.65121224537</v>
       </c>
@@ -1482,14 +1728,29 @@
       <c r="U15">
         <v>567.5926343368042</v>
       </c>
-      <c r="V15">
-        <v>5.000659156946822</v>
-      </c>
-      <c r="W15" t="b">
-        <v>0</v>
+      <c r="V15" t="b">
+        <v>1</v>
+      </c>
+      <c r="X15">
+        <v>0.254246132</v>
+      </c>
+      <c r="Y15">
+        <v>0.263088472</v>
+      </c>
+      <c r="Z15">
+        <v>0.3658642367549146</v>
+      </c>
+      <c r="AA15">
+        <v>4.421169999999996</v>
+      </c>
+      <c r="AB15">
+        <v>0.08335482832111547</v>
+      </c>
+      <c r="AC15">
+        <v>47.31158659147398</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:29">
       <c r="A16" s="1">
         <v>46068.65132798611</v>
       </c>
@@ -1553,14 +1814,29 @@
       <c r="U16">
         <v>569.3124738446322</v>
       </c>
-      <c r="V16">
-        <v>2.63397522236627</v>
-      </c>
-      <c r="W16" t="b">
+      <c r="V16" t="b">
         <v>1</v>
       </c>
+      <c r="X16">
+        <v>0.254279836</v>
+      </c>
+      <c r="Y16">
+        <v>0.263122538</v>
+      </c>
+      <c r="Z16">
+        <v>0.3659121547581446</v>
+      </c>
+      <c r="AA16">
+        <v>4.421351000000001</v>
+      </c>
+      <c r="AB16">
+        <v>0.08336222467191538</v>
+      </c>
+      <c r="AC16">
+        <v>47.45915435316018</v>
+      </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:29">
       <c r="A17" s="1">
         <v>46068.65144430556</v>
       </c>
@@ -1624,14 +1900,29 @@
       <c r="U17">
         <v>563.8618450074487</v>
       </c>
-      <c r="V17">
-        <v>2.786455085870701</v>
-      </c>
-      <c r="W17" t="b">
+      <c r="V17" t="b">
         <v>1</v>
       </c>
+      <c r="X17">
+        <v>0.25430114</v>
+      </c>
+      <c r="Y17">
+        <v>0.26315342</v>
+      </c>
+      <c r="Z17">
+        <v>0.3659491662280377</v>
+      </c>
+      <c r="AA17">
+        <v>4.426139999999997</v>
+      </c>
+      <c r="AB17">
+        <v>0.08328162845073561</v>
+      </c>
+      <c r="AC17">
+        <v>46.95933267345661</v>
+      </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:29">
       <c r="A18" s="1">
         <v>46068.6515600463</v>
       </c>
@@ -1695,11 +1986,26 @@
       <c r="U18">
         <v>571.4078860941512</v>
       </c>
-      <c r="V18">
-        <v>3.895357135924028</v>
-      </c>
-      <c r="W18" t="b">
-        <v>0</v>
+      <c r="V18" t="b">
+        <v>1</v>
+      </c>
+      <c r="X18">
+        <v>0.25431068</v>
+      </c>
+      <c r="Y18">
+        <v>0.263181118</v>
+      </c>
+      <c r="Z18">
+        <v>0.3659757134480269</v>
+      </c>
+      <c r="AA18">
+        <v>4.435218999999996</v>
+      </c>
+      <c r="AB18">
+        <v>0.08311955146195676</v>
+      </c>
+      <c r="AC18">
+        <v>47.49516719397073</v>
       </c>
     </row>
   </sheetData>
